--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\white\babySchmaby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF696262-F6ED-416C-9ABC-4F9F8942D5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0FB5FF-2D4A-4192-B195-BF84B32ABB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2543" yWindow="2543" windowWidth="16200" windowHeight="9307" activeTab="1" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
+    <workbookView xWindow="2543" yWindow="2543" windowWidth="16200" windowHeight="9307" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
   </bookViews>
   <sheets>
     <sheet name="income" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="9">
   <si>
     <t>date</t>
   </si>
@@ -436,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5524CBEA-DFC5-499C-9C65-2975C259AA4B}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2">
         <f>SUM(C:C) - SUM(expense!C:C)</f>
-        <v>158.19</v>
+        <v>166.19</v>
       </c>
       <c r="E2">
         <f>SUMIF(B:B, "&lt;&gt;personal", C:C) - SUM(expense!C:C)</f>
@@ -517,6 +517,17 @@
       </c>
       <c r="C6">
         <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -555,7 +566,7 @@
       </c>
       <c r="D2">
         <f>SUM(income!C:C) - SUM(C:C)</f>
-        <v>158.19</v>
+        <v>166.19</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">

--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\white\babySchmaby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0FB5FF-2D4A-4192-B195-BF84B32ABB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BD9CA0-C693-47C1-ABCD-BBD9B665706D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2543" yWindow="2543" windowWidth="16200" windowHeight="9307" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="16200" windowHeight="9308" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
   </bookViews>
   <sheets>
     <sheet name="income" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
   <si>
     <t>date</t>
   </si>
@@ -468,11 +468,11 @@
       </c>
       <c r="D2">
         <f>SUM(C:C) - SUM(expense!C:C)</f>
-        <v>166.19</v>
+        <v>136.55000000000001</v>
       </c>
       <c r="E2">
         <f>SUMIF(B:B, "&lt;&gt;personal", C:C) - SUM(expense!C:C)</f>
-        <v>-271.81</v>
+        <v>-301.45</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -537,7 +537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CA7448-F594-4990-B330-5741336B78F2}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -566,7 +566,7 @@
       </c>
       <c r="D2">
         <f>SUM(income!C:C) - SUM(C:C)</f>
-        <v>166.19</v>
+        <v>136.55000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -611,6 +611,17 @@
       </c>
       <c r="C6">
         <v>11.76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>29.64</v>
       </c>
     </row>
   </sheetData>

--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\white\babySchmaby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BD9CA0-C693-47C1-ABCD-BBD9B665706D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CDA691-64F9-4CD5-9AD9-E450C5A760F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="16200" windowHeight="9308" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="9">
   <si>
     <t>date</t>
   </si>
@@ -468,11 +468,11 @@
       </c>
       <c r="D2">
         <f>SUM(C:C) - SUM(expense!C:C)</f>
-        <v>136.55000000000001</v>
+        <v>90.350000000000023</v>
       </c>
       <c r="E2">
         <f>SUMIF(B:B, "&lt;&gt;personal", C:C) - SUM(expense!C:C)</f>
-        <v>-301.45</v>
+        <v>-347.65</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -537,7 +537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CA7448-F594-4990-B330-5741336B78F2}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -566,7 +566,7 @@
       </c>
       <c r="D2">
         <f>SUM(income!C:C) - SUM(C:C)</f>
-        <v>136.55000000000001</v>
+        <v>90.350000000000023</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -622,6 +622,17 @@
       </c>
       <c r="C7">
         <v>29.64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>46.2</v>
       </c>
     </row>
   </sheetData>

--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\white\babySchmaby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CDA691-64F9-4CD5-9AD9-E450C5A760F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3901BEC9-0525-4ADF-8E00-DC2049C722E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="16200" windowHeight="9308" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
   </bookViews>
   <sheets>
     <sheet name="income" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="9">
   <si>
     <t>date</t>
   </si>
@@ -436,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5524CBEA-DFC5-499C-9C65-2975C259AA4B}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2">
         <f>SUM(C:C) - SUM(expense!C:C)</f>
-        <v>90.350000000000023</v>
+        <v>220.35000000000002</v>
       </c>
       <c r="E2">
         <f>SUMIF(B:B, "&lt;&gt;personal", C:C) - SUM(expense!C:C)</f>
@@ -528,6 +528,17 @@
       </c>
       <c r="C7">
         <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -566,7 +577,7 @@
       </c>
       <c r="D2">
         <f>SUM(income!C:C) - SUM(C:C)</f>
-        <v>90.350000000000023</v>
+        <v>220.35000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">

--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3901BEC9-0525-4ADF-8E00-DC2049C722E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
   </bookViews>
   <sheets>
     <sheet name="income" sheetId="1" r:id="rId1"/>

--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\white\babySchmaby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3901BEC9-0525-4ADF-8E00-DC2049C722E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6255437-2D34-4360-81D0-AC138A3E02E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
+    <workbookView xWindow="11648" yWindow="0" windowWidth="10035" windowHeight="12863" activeTab="1" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
   </bookViews>
   <sheets>
     <sheet name="income" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="10">
   <si>
     <t>date</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>amazon</t>
+  </si>
+  <si>
+    <t>bambulab</t>
   </si>
 </sst>
 </file>
@@ -468,11 +471,11 @@
       </c>
       <c r="D2">
         <f>SUM(C:C) - SUM(expense!C:C)</f>
-        <v>220.35000000000002</v>
+        <v>47.450000000000045</v>
       </c>
       <c r="E2">
         <f>SUMIF(B:B, "&lt;&gt;personal", C:C) - SUM(expense!C:C)</f>
-        <v>-347.65</v>
+        <v>-520.54999999999995</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -548,7 +551,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CA7448-F594-4990-B330-5741336B78F2}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -577,7 +580,7 @@
       </c>
       <c r="D2">
         <f>SUM(income!C:C) - SUM(C:C)</f>
-        <v>220.35000000000002</v>
+        <v>47.450000000000045</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -644,6 +647,17 @@
       </c>
       <c r="C8">
         <v>46.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>172.9</v>
       </c>
     </row>
   </sheetData>

--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\white\babySchmaby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6255437-2D34-4360-81D0-AC138A3E02E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD752E18-56FD-4F19-8D12-3331EB1D5FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11648" yWindow="0" windowWidth="10035" windowHeight="12863" activeTab="1" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="1" xr2:uid="{C518DA8D-1D27-42E8-B41E-3BECF69F971A}"/>
   </bookViews>
   <sheets>
     <sheet name="income" sheetId="1" r:id="rId1"/>
